--- a/human_validation/judge/kor/judge_D003_S003_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S003_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,103 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 계속 안절부절못하는 느낌이 들어요, 마치 너무 팽팽하게 감겨서 제대로 진정이 안 되는 것 같아요. 계획 회의에서 차분히 앉아 있어야 할 때나, 그림을 그리거나 요가를 할 때도 여전히 그런 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 안절부절못함과 더불어, 일상적인 일들에 대해 지속적이거나 지나친 걱정을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 일상적인 일들에 대해 걱정을 많이 느낀 적은 딱히 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 어린 시절에도 이런 안절부절못함을 경험하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 초등학교 때, 계속 자리에서 일어나고, 다른 아이들 말에 끼어들고, 선생님이 질문을 끝내기도 전에 답을 불쑥 말해서 가정통신문을 받곤 했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 일에 집중을 유지하는 데 자주 어려움을 겪으시거나, 직장이나 일상에서 부주의한 실수를 하시는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 최근 몇 년 동안, 거래처 스프레드시트를 꼼꼼히 확인했다고 생각하는데, 나중에 기획 코디네이터가 뭔가를 찾아내요. 예를 들면 제가 SKU를 뒤바꿔 입력했거나, 운송 추가 요금을 빠뜨렸거나, 발주서에 수량을 잘못 입력했거나 하는 식으로요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)
 인구통계: 성별 여성 / 나이 51 / 직업상태 wholesale or retail buyer / 최종학력 학사
@@ -575,161 +663,42 @@
 증상 지속 기간: 2 years and 2 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S012
-배경 서술: 이사벨라의 증상은 시댁과의 갈등이 오래 이어지던 시기에 뚜렷해졌다. 가족 부양의 의무와 재정 문제를 둘러싼 다툼이 그녀가 그동안 요가와 그림, 세심한 구매 기획을 위해 지켜왔던 저녁 시간을 잠식하기 시작했다. 2년 2개월에 걸쳐, 늘어난 스트레스는 오래전부터 있어 왔던 성향들을 감당하기 더 어렵게 만들었다. 그녀는 거래처 스프레드시트에서 세부사항을 놓쳤고, 조달 회의에서 직접적인 질문을 제대로 받아들이지 못하는 것처럼 보였으며, 통화 중 계속 꼼지락거렸고, 협상 중 상대가 말을 끝내기도 전에 불쑥 대답했다. 장애는 경미한 수준에 머물렀지만 실제로 존재했다. 수정된 발주서 오류, 긴장된 가족 저녁 식사, 그리고 멘토링하려던 후배 동료의 말을 끊는다는 피드백으로 나타났다. 그녀는 직장, 집, 그리고 자신이 하던 STEM 멘토링 시간에서 같은 패턴을 알아차린 후, 1차 진료 웰니스 방문 중 직접 이 문제를 언급했고 정신과 평가를 의뢰받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 계속 안절부절못하는 느낌이 들어요, 마치 너무 팽팽하게 감겨서 제대로 진정이 안 되는 것 같아요. 계획 회의에서 차분히 앉아 있어야 할 때나, 그림을 그리거나 요가를 할 때도 여전히 그런 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 안절부절못함과 더불어, 일상적인 일들에 대해 지속적이거나 지나친 걱정을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 일상적인 일들에 대해 걱정을 많이 느낀 적은 딱히 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 어린 시절에도 이런 안절부절못함을 경험하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 초등학교 때, 계속 자리에서 일어나고, 다른 아이들 말에 끼어들고, 선생님이 질문을 끝내기도 전에 답을 불쑥 말해서 가정통신문을 받곤 했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 일에 집중을 유지하는 데 자주 어려움을 겪으시거나, 직장이나 일상에서 부주의한 실수를 하시는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 최근 몇 년 동안, 거래처 스프레드시트를 꼼꼼히 확인했다고 생각하는데, 나중에 기획 코디네이터가 뭔가를 찾아내요. 예를 들면 제가 SKU를 뒤바꿔 입력했거나, 운송 추가 요금을 빠뜨렸거나, 발주서에 수량을 잘못 입력했거나 하는 식으로요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 이사벨라의 증상은 시댁과의 갈등이 오래 이어지던 시기에 뚜렷해졌다. 가족 부양의 의무와 재정 문제를 둘러싼 다툼이 그녀가 그동안 요가와 그림, 세심한 구매 기획을 위해 지켜왔던 저녁 시간을 잠식하기 시작했다. 2년 2개월에 걸쳐, 늘어난 스트레스는 오래전부터 있어 왔던 성향들을 감당하기 더 어렵게 만들었다. 그녀는 거래처 스프레드시트에서 세부사항을 놓쳤고, 조달 회의에서 직접적인 질문을 제대로 받아들이지 못하는 것처럼 보였으며, 통화 중 계속 꼼지락거렸고, 협상 중 상대가 말을 끝내기도 전에 불쑥 대답했다. 장애는 경미한 수준에 머물렀지만 실제로 존재했다. 수정된 발주서 오류, 긴장된 가족 저녁 식사, 그리고 멘토링하려던 후배 동료의 말을 끊는다는 피드백으로 나타났다. 그녀는 직장, 집, 그리고 자신이 하던 STEM 멘토링 시간에서 같은 패턴을 알아차린 후, 1차 진료 웰니스 방문 중 직접 이 문제를 언급했고 정신과 평가를 의뢰받았다.
+표집된 증상 목록:
+  - S001 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - S003 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
+  - S010 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - S011 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - S012 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - S014 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.
+  - S016 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
+  - S018 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (복합형) (D001, ICD: F90.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
-  누락: 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (복합형) (D001, ICD: F90.2)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.
+  - 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S003_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S003_P003__gemini-3.8-flash_kor.xlsx
@@ -649,6 +649,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -694,11 +699,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S003_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S003_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.4166</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.875</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
